--- a/web/public/forms/gongjeong-inryeok.xlsx
+++ b/web/public/forms/gongjeong-inryeok.xlsx
@@ -659,7 +659,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="26" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="26" t="inlineStr">
@@ -6283,7 +6283,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="26" t="inlineStr">

--- a/web/public/forms/gongjeong-inryeok.xlsx
+++ b/web/public/forms/gongjeong-inryeok.xlsx
@@ -629,7 +629,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
